--- a/Inlet_outlet_turbidity_dosing_ details.xlsx
+++ b/Inlet_outlet_turbidity_dosing_ details.xlsx
@@ -478,10 +478,10 @@
         <v>322</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>15.4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="3">
@@ -502,10 +502,10 @@
         <v>322</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>17.9</v>
       </c>
       <c r="F3" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         <v>323</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>17.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="5">
@@ -550,10 +550,10 @@
         <v>323</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>16.9</v>
       </c>
       <c r="F5" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -574,10 +574,10 @@
         <v>323</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -598,10 +598,10 @@
         <v>324</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -622,10 +622,10 @@
         <v>324</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -646,10 +646,10 @@
         <v>324</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -670,10 +670,10 @@
         <v>324</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>17.7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="11">
@@ -694,10 +694,10 @@
         <v>325</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -718,10 +718,10 @@
         <v>325</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>15.7</v>
       </c>
       <c r="F12" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="13">
@@ -742,10 +742,10 @@
         <v>325</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>19.6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -766,10 +766,10 @@
         <v>325</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>19.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
@@ -790,10 +790,10 @@
         <v>326</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>16.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
@@ -814,10 +814,10 @@
         <v>326</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>16.7</v>
       </c>
       <c r="F16" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="17">
@@ -838,10 +838,10 @@
         <v>326</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>16.8</v>
       </c>
       <c r="F17" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
@@ -862,10 +862,10 @@
         <v>326</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="F18" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="19">
@@ -886,10 +886,10 @@
         <v>326</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="F19" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="20">
@@ -910,10 +910,10 @@
         <v>326</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>17.9</v>
       </c>
       <c r="F20" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
@@ -934,10 +934,10 @@
         <v>326</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>17.4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -958,10 +958,10 @@
         <v>326</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
       <c r="F22" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="23">
@@ -982,10 +982,10 @@
         <v>326</v>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>16.7</v>
       </c>
       <c r="F23" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="24">
@@ -1006,10 +1006,10 @@
         <v>326</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="25">
@@ -1030,10 +1030,10 @@
         <v>326</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="F25" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="26">
@@ -1054,10 +1054,10 @@
         <v>326</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="F26" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -1078,10 +1078,10 @@
         <v>325</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="28">
@@ -1102,10 +1102,10 @@
         <v>325</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="29">
@@ -1126,10 +1126,10 @@
         <v>325</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="F29" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="30">
@@ -1150,10 +1150,10 @@
         <v>325</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>17.9</v>
       </c>
       <c r="F30" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="31">
@@ -1174,10 +1174,10 @@
         <v>325</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="32">
@@ -1198,10 +1198,10 @@
         <v>324</v>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>17.7</v>
       </c>
       <c r="F32" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="33">
@@ -1222,10 +1222,10 @@
         <v>324</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>15.8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="34">
@@ -1246,10 +1246,10 @@
         <v>324</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="F34" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="35">
@@ -1270,10 +1270,10 @@
         <v>324</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
       <c r="F35" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="36">
@@ -1294,10 +1294,10 @@
         <v>323</v>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="37">
@@ -1318,10 +1318,10 @@
         <v>323</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>17.7</v>
       </c>
       <c r="F37" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38">
@@ -1342,10 +1342,10 @@
         <v>323</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>15.4</v>
       </c>
       <c r="F38" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39">
@@ -1366,10 +1366,10 @@
         <v>322</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>14.4</v>
       </c>
       <c r="F39" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="40">
@@ -1390,10 +1390,10 @@
         <v>322</v>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="F40" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="41">
@@ -1414,10 +1414,10 @@
         <v>322</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>15.4</v>
       </c>
       <c r="F41" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="42">
@@ -1438,10 +1438,10 @@
         <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F42" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="43">
@@ -1462,10 +1462,10 @@
         <v>321</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="F43" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
@@ -1486,10 +1486,10 @@
         <v>321</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
@@ -1510,10 +1510,10 @@
         <v>320</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="F45" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="46">
@@ -1534,10 +1534,10 @@
         <v>320</v>
       </c>
       <c r="E46" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
@@ -1558,10 +1558,10 @@
         <v>320</v>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="48">
@@ -1582,10 +1582,10 @@
         <v>319</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="49">
@@ -1606,10 +1606,10 @@
         <v>319</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="50">
@@ -1630,10 +1630,10 @@
         <v>319</v>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -1654,10 +1654,10 @@
         <v>319</v>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="F51" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="52">
@@ -1678,10 +1678,10 @@
         <v>319</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="F52" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="53">
@@ -1702,10 +1702,10 @@
         <v>318</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="F53" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="54">
@@ -1726,10 +1726,10 @@
         <v>318</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="55">
@@ -1750,10 +1750,10 @@
         <v>318</v>
       </c>
       <c r="E55" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="F55" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="56">
@@ -1774,10 +1774,10 @@
         <v>318</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="57">
@@ -1798,10 +1798,10 @@
         <v>318</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="F57" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="58">
@@ -1822,10 +1822,10 @@
         <v>318</v>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F58" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="59">
@@ -1846,10 +1846,10 @@
         <v>318</v>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="F59" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="60">
@@ -1870,10 +1870,10 @@
         <v>318</v>
       </c>
       <c r="E60" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="F60" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="61">
@@ -1894,10 +1894,10 @@
         <v>348</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="F61" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="62">
@@ -1918,10 +1918,10 @@
         <v>349</v>
       </c>
       <c r="E62" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="F62" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="63">
@@ -1942,10 +1942,10 @@
         <v>350</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>17.2</v>
       </c>
       <c r="F63" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="64">
@@ -1966,10 +1966,10 @@
         <v>351</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>19.8</v>
       </c>
       <c r="F64" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="65">
@@ -1990,10 +1990,10 @@
         <v>351</v>
       </c>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>18.2</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="66">
@@ -2014,10 +2014,10 @@
         <v>352</v>
       </c>
       <c r="E66" t="n">
-        <v>12</v>
+        <v>18.1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="67">
@@ -2038,10 +2038,10 @@
         <v>352</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>19.3</v>
       </c>
       <c r="F67" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="68">
@@ -2062,10 +2062,10 @@
         <v>352</v>
       </c>
       <c r="E68" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="F68" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="69">
@@ -2086,10 +2086,10 @@
         <v>353</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>20.6</v>
       </c>
       <c r="F69" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="70">
@@ -2110,10 +2110,10 @@
         <v>353</v>
       </c>
       <c r="E70" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="F70" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="71">
@@ -2134,10 +2134,10 @@
         <v>353</v>
       </c>
       <c r="E71" t="n">
-        <v>12</v>
+        <v>21.7</v>
       </c>
       <c r="F71" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="72">
@@ -2158,10 +2158,10 @@
         <v>354</v>
       </c>
       <c r="E72" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F72" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="73">
@@ -2182,10 +2182,10 @@
         <v>354</v>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>18.9</v>
       </c>
       <c r="F73" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="74">
@@ -2206,10 +2206,10 @@
         <v>355</v>
       </c>
       <c r="E74" t="n">
-        <v>12</v>
+        <v>18.4</v>
       </c>
       <c r="F74" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="75">
@@ -2230,10 +2230,10 @@
         <v>355</v>
       </c>
       <c r="E75" t="n">
-        <v>18</v>
+        <v>29.5</v>
       </c>
       <c r="F75" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="76">
@@ -2254,10 +2254,10 @@
         <v>356</v>
       </c>
       <c r="E76" t="n">
-        <v>18</v>
+        <v>29.4</v>
       </c>
       <c r="F76" t="n">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="77">
@@ -2278,10 +2278,10 @@
         <v>357</v>
       </c>
       <c r="E77" t="n">
-        <v>18</v>
+        <v>29.9</v>
       </c>
       <c r="F77" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="78">
@@ -2302,10 +2302,10 @@
         <v>358</v>
       </c>
       <c r="E78" t="n">
-        <v>18</v>
+        <v>30.4</v>
       </c>
       <c r="F78" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="79">
@@ -2326,10 +2326,10 @@
         <v>358</v>
       </c>
       <c r="E79" t="n">
-        <v>18</v>
+        <v>27.9</v>
       </c>
       <c r="F79" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="80">
@@ -2350,10 +2350,10 @@
         <v>358</v>
       </c>
       <c r="E80" t="n">
-        <v>18</v>
+        <v>29.2</v>
       </c>
       <c r="F80" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="81">
@@ -2374,10 +2374,10 @@
         <v>359</v>
       </c>
       <c r="E81" t="n">
-        <v>18</v>
+        <v>28.4</v>
       </c>
       <c r="F81" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="82">
@@ -2398,10 +2398,10 @@
         <v>359</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>31.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="83">
@@ -2422,10 +2422,10 @@
         <v>358</v>
       </c>
       <c r="E83" t="n">
-        <v>18</v>
+        <v>30.3</v>
       </c>
       <c r="F83" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="84">
@@ -2446,10 +2446,10 @@
         <v>358</v>
       </c>
       <c r="E84" t="n">
-        <v>18</v>
+        <v>28.9</v>
       </c>
       <c r="F84" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="85">
@@ -2470,10 +2470,10 @@
         <v>357</v>
       </c>
       <c r="E85" t="n">
-        <v>18</v>
+        <v>27.5</v>
       </c>
       <c r="F85" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="86">
@@ -2494,10 +2494,10 @@
         <v>357</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>28.2</v>
       </c>
       <c r="F86" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="87">
@@ -2518,10 +2518,10 @@
         <v>356</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>27.8</v>
       </c>
       <c r="F87" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="88">
@@ -2542,10 +2542,10 @@
         <v>355</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>28.9</v>
       </c>
       <c r="F88" t="n">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="89">
@@ -2566,10 +2566,10 @@
         <v>354</v>
       </c>
       <c r="E89" t="n">
-        <v>12</v>
+        <v>20.7</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="90">
@@ -2590,10 +2590,10 @@
         <v>353</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>21.3</v>
       </c>
       <c r="F90" t="n">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="91">
@@ -2614,10 +2614,10 @@
         <v>353</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>19.3</v>
       </c>
       <c r="F91" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="92">
@@ -2638,10 +2638,10 @@
         <v>352</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="F92" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="93">
@@ -2662,10 +2662,10 @@
         <v>351</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>19.7</v>
       </c>
       <c r="F93" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="94">
@@ -2686,10 +2686,10 @@
         <v>351</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>19.6</v>
       </c>
       <c r="F94" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="95">
@@ -2710,10 +2710,10 @@
         <v>350</v>
       </c>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
       <c r="F95" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="96">
@@ -2734,10 +2734,10 @@
         <v>350</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>19.3</v>
       </c>
       <c r="F96" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="97">
@@ -2758,10 +2758,10 @@
         <v>350</v>
       </c>
       <c r="E97" t="n">
-        <v>12</v>
+        <v>18.1</v>
       </c>
       <c r="F97" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="98">
@@ -2782,10 +2782,10 @@
         <v>349</v>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F98" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="99">
@@ -2806,7 +2806,7 @@
         <v>349</v>
       </c>
       <c r="E99" t="n">
-        <v>12</v>
+        <v>17.4</v>
       </c>
       <c r="F99" t="n">
         <v>0.19</v>
@@ -2830,10 +2830,10 @@
         <v>348</v>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="F100" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="101">
@@ -2854,10 +2854,10 @@
         <v>348</v>
       </c>
       <c r="E101" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="F101" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="102">
@@ -2878,10 +2878,10 @@
         <v>347</v>
       </c>
       <c r="E102" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F102" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="103">
@@ -2902,10 +2902,10 @@
         <v>346</v>
       </c>
       <c r="E103" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="104">
@@ -2926,10 +2926,10 @@
         <v>345</v>
       </c>
       <c r="E104" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="F104" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="105">
@@ -2950,10 +2950,10 @@
         <v>345</v>
       </c>
       <c r="E105" t="n">
-        <v>12</v>
+        <v>15.7</v>
       </c>
       <c r="F105" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="106">
@@ -2974,10 +2974,10 @@
         <v>344</v>
       </c>
       <c r="E106" t="n">
-        <v>12</v>
+        <v>16.9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="107">
@@ -2998,10 +2998,10 @@
         <v>343</v>
       </c>
       <c r="E107" t="n">
-        <v>12</v>
+        <v>13.9</v>
       </c>
       <c r="F107" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="108">
@@ -3022,10 +3022,10 @@
         <v>342</v>
       </c>
       <c r="E108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F108" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="109">
@@ -3046,10 +3046,10 @@
         <v>342</v>
       </c>
       <c r="E109" t="n">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="F109" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="110">
@@ -3073,7 +3073,7 @@
         <v>8</v>
       </c>
       <c r="F110" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="111">
@@ -3094,10 +3094,10 @@
         <v>341</v>
       </c>
       <c r="E111" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="F111" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="112">
@@ -3118,10 +3118,10 @@
         <v>341</v>
       </c>
       <c r="E112" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="113">
@@ -3142,10 +3142,10 @@
         <v>342</v>
       </c>
       <c r="E113" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F113" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="114">
@@ -3166,10 +3166,10 @@
         <v>342</v>
       </c>
       <c r="E114" t="n">
-        <v>8</v>
+        <v>11.1</v>
       </c>
       <c r="F114" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="115">
@@ -3190,10 +3190,10 @@
         <v>343</v>
       </c>
       <c r="E115" t="n">
-        <v>12</v>
+        <v>16.1</v>
       </c>
       <c r="F115" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="116">
@@ -3214,10 +3214,10 @@
         <v>343</v>
       </c>
       <c r="E116" t="n">
-        <v>12</v>
+        <v>15.7</v>
       </c>
       <c r="F116" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="117">
@@ -3238,10 +3238,10 @@
         <v>344</v>
       </c>
       <c r="E117" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F117" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="118">
@@ -3262,10 +3262,10 @@
         <v>345</v>
       </c>
       <c r="E118" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F118" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="119">
@@ -3286,10 +3286,10 @@
         <v>345</v>
       </c>
       <c r="E119" t="n">
-        <v>12</v>
+        <v>14.9</v>
       </c>
       <c r="F119" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="120">
@@ -3310,10 +3310,10 @@
         <v>346</v>
       </c>
       <c r="E120" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F120" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="121">
@@ -3334,10 +3334,10 @@
         <v>347</v>
       </c>
       <c r="E121" t="n">
-        <v>12</v>
+        <v>16.8</v>
       </c>
       <c r="F121" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="122">
@@ -3358,10 +3358,10 @@
         <v>347</v>
       </c>
       <c r="E122" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F122" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="123">
@@ -3382,10 +3382,10 @@
         <v>347</v>
       </c>
       <c r="E123" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="F123" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="124">
@@ -3406,10 +3406,10 @@
         <v>348</v>
       </c>
       <c r="E124" t="n">
-        <v>12</v>
+        <v>16.3</v>
       </c>
       <c r="F124" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="125">
@@ -3430,10 +3430,10 @@
         <v>348</v>
       </c>
       <c r="E125" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="F125" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="126">
@@ -3454,10 +3454,10 @@
         <v>348</v>
       </c>
       <c r="E126" t="n">
-        <v>12</v>
+        <v>16.3</v>
       </c>
       <c r="F126" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="127">
@@ -3478,10 +3478,10 @@
         <v>349</v>
       </c>
       <c r="E127" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="F127" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="128">
@@ -3502,10 +3502,10 @@
         <v>349</v>
       </c>
       <c r="E128" t="n">
-        <v>12</v>
+        <v>19.1</v>
       </c>
       <c r="F128" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="129">
@@ -3526,10 +3526,10 @@
         <v>350</v>
       </c>
       <c r="E129" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="F129" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="130">
@@ -3550,10 +3550,10 @@
         <v>351</v>
       </c>
       <c r="E130" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="F130" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="131">
@@ -3574,10 +3574,10 @@
         <v>351</v>
       </c>
       <c r="E131" t="n">
-        <v>12</v>
+        <v>18.9</v>
       </c>
       <c r="F131" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="132">
@@ -3598,10 +3598,10 @@
         <v>352</v>
       </c>
       <c r="E132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F132" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="133">
@@ -3622,10 +3622,10 @@
         <v>353</v>
       </c>
       <c r="E133" t="n">
-        <v>12</v>
+        <v>18.7</v>
       </c>
       <c r="F133" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="134">
@@ -3646,10 +3646,10 @@
         <v>354</v>
       </c>
       <c r="E134" t="n">
-        <v>12</v>
+        <v>18.7</v>
       </c>
       <c r="F134" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="135">
@@ -3670,10 +3670,10 @@
         <v>355</v>
       </c>
       <c r="E135" t="n">
-        <v>18</v>
+        <v>27.6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="136">
@@ -3694,10 +3694,10 @@
         <v>356</v>
       </c>
       <c r="E136" t="n">
-        <v>18</v>
+        <v>30.5</v>
       </c>
       <c r="F136" t="n">
-        <v>0.41</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="137">
@@ -3718,10 +3718,10 @@
         <v>357</v>
       </c>
       <c r="E137" t="n">
-        <v>18</v>
+        <v>28.4</v>
       </c>
       <c r="F137" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="138">
@@ -3742,10 +3742,10 @@
         <v>358</v>
       </c>
       <c r="E138" t="n">
-        <v>18</v>
+        <v>29.5</v>
       </c>
       <c r="F138" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="139">
@@ -3766,10 +3766,10 @@
         <v>358</v>
       </c>
       <c r="E139" t="n">
-        <v>18</v>
+        <v>30.4</v>
       </c>
       <c r="F139" t="n">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="140">
@@ -3790,10 +3790,10 @@
         <v>358</v>
       </c>
       <c r="E140" t="n">
-        <v>18</v>
+        <v>29.1</v>
       </c>
       <c r="F140" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141">
@@ -3814,10 +3814,10 @@
         <v>358</v>
       </c>
       <c r="E141" t="n">
-        <v>18</v>
+        <v>31.5</v>
       </c>
       <c r="F141" t="n">
-        <v>0.44</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="142">
@@ -3838,10 +3838,10 @@
         <v>358</v>
       </c>
       <c r="E142" t="n">
-        <v>18</v>
+        <v>31.4</v>
       </c>
       <c r="F142" t="n">
-        <v>0.44</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="143">
@@ -3862,10 +3862,10 @@
         <v>358</v>
       </c>
       <c r="E143" t="n">
-        <v>18</v>
+        <v>28.4</v>
       </c>
       <c r="F143" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="144">
@@ -3886,10 +3886,10 @@
         <v>357</v>
       </c>
       <c r="E144" t="n">
-        <v>18</v>
+        <v>29.1</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="145">
@@ -3910,10 +3910,10 @@
         <v>357</v>
       </c>
       <c r="E145" t="n">
-        <v>18</v>
+        <v>28.1</v>
       </c>
       <c r="F145" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="146">
@@ -3934,10 +3934,10 @@
         <v>356</v>
       </c>
       <c r="E146" t="n">
-        <v>18</v>
+        <v>27.8</v>
       </c>
       <c r="F146" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="147">
@@ -3958,10 +3958,10 @@
         <v>356</v>
       </c>
       <c r="E147" t="n">
-        <v>18</v>
+        <v>26.6</v>
       </c>
       <c r="F147" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="148">
@@ -3982,10 +3982,10 @@
         <v>355</v>
       </c>
       <c r="E148" t="n">
-        <v>18</v>
+        <v>28.7</v>
       </c>
       <c r="F148" t="n">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="149">
@@ -4006,10 +4006,10 @@
         <v>355</v>
       </c>
       <c r="E149" t="n">
-        <v>18</v>
+        <v>28.1</v>
       </c>
       <c r="F149" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="150">
@@ -4030,10 +4030,10 @@
         <v>355</v>
       </c>
       <c r="E150" t="n">
-        <v>12</v>
+        <v>18.7</v>
       </c>
       <c r="F150" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="151">
@@ -4054,10 +4054,10 @@
         <v>355</v>
       </c>
       <c r="E151" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="F151" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="152">
@@ -4078,10 +4078,10 @@
         <v>355</v>
       </c>
       <c r="E152" t="n">
-        <v>12</v>
+        <v>21.9</v>
       </c>
       <c r="F152" t="n">
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="153">
@@ -4102,10 +4102,10 @@
         <v>354</v>
       </c>
       <c r="E153" t="n">
-        <v>12</v>
+        <v>19.2</v>
       </c>
       <c r="F153" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="154">
@@ -4126,10 +4126,10 @@
         <v>354</v>
       </c>
       <c r="E154" t="n">
-        <v>12</v>
+        <v>18.7</v>
       </c>
       <c r="F154" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155">
@@ -4150,10 +4150,10 @@
         <v>354</v>
       </c>
       <c r="E155" t="n">
-        <v>12</v>
+        <v>19.9</v>
       </c>
       <c r="F155" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="156">
@@ -4174,10 +4174,10 @@
         <v>353</v>
       </c>
       <c r="E156" t="n">
-        <v>12</v>
+        <v>21.7</v>
       </c>
       <c r="F156" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="157">
@@ -4198,10 +4198,10 @@
         <v>353</v>
       </c>
       <c r="E157" t="n">
-        <v>12</v>
+        <v>18.4</v>
       </c>
       <c r="F157" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="158">
@@ -4222,10 +4222,10 @@
         <v>352</v>
       </c>
       <c r="E158" t="n">
-        <v>12</v>
+        <v>19.8</v>
       </c>
       <c r="F158" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="159">
@@ -4246,10 +4246,10 @@
         <v>351</v>
       </c>
       <c r="E159" t="n">
-        <v>12</v>
+        <v>19.8</v>
       </c>
       <c r="F159" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="160">
@@ -4270,10 +4270,10 @@
         <v>350</v>
       </c>
       <c r="E160" t="n">
-        <v>12</v>
+        <v>17.2</v>
       </c>
       <c r="F160" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="161">
@@ -4294,10 +4294,10 @@
         <v>349</v>
       </c>
       <c r="E161" t="n">
-        <v>12</v>
+        <v>18.7</v>
       </c>
       <c r="F161" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="162">
@@ -4318,10 +4318,10 @@
         <v>348</v>
       </c>
       <c r="E162" t="n">
-        <v>12</v>
+        <v>16.7</v>
       </c>
       <c r="F162" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="163">
@@ -4342,10 +4342,10 @@
         <v>347</v>
       </c>
       <c r="E163" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="F163" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="164">
@@ -4366,10 +4366,10 @@
         <v>346</v>
       </c>
       <c r="E164" t="n">
-        <v>12</v>
+        <v>16.8</v>
       </c>
       <c r="F164" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="165">
@@ -4390,10 +4390,10 @@
         <v>345</v>
       </c>
       <c r="E165" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F165" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="166">
@@ -4414,7 +4414,7 @@
         <v>344</v>
       </c>
       <c r="E166" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="F166" t="n">
         <v>0.15</v>
@@ -4438,10 +4438,10 @@
         <v>343</v>
       </c>
       <c r="E167" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="F167" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="168">
@@ -4462,10 +4462,10 @@
         <v>343</v>
       </c>
       <c r="E168" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
       <c r="F168" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="169">
@@ -4486,7 +4486,7 @@
         <v>343</v>
       </c>
       <c r="E169" t="n">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="F169" t="n">
         <v>0.15</v>
@@ -4510,10 +4510,10 @@
         <v>343</v>
       </c>
       <c r="E170" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F170" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="171">
@@ -4534,10 +4534,10 @@
         <v>343</v>
       </c>
       <c r="E171" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="F171" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="172">
@@ -4558,10 +4558,10 @@
         <v>343</v>
       </c>
       <c r="E172" t="n">
-        <v>12</v>
+        <v>15.7</v>
       </c>
       <c r="F172" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="173">
@@ -4582,10 +4582,10 @@
         <v>343</v>
       </c>
       <c r="E173" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="F173" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="174">
@@ -4606,10 +4606,10 @@
         <v>343</v>
       </c>
       <c r="E174" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="F174" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="175">
@@ -4630,10 +4630,10 @@
         <v>344</v>
       </c>
       <c r="E175" t="n">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="F175" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="176">
@@ -4654,10 +4654,10 @@
         <v>344</v>
       </c>
       <c r="E176" t="n">
-        <v>12</v>
+        <v>15.9</v>
       </c>
       <c r="F176" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="177">
@@ -4678,10 +4678,10 @@
         <v>344</v>
       </c>
       <c r="E177" t="n">
-        <v>12</v>
+        <v>14.1</v>
       </c>
       <c r="F177" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="178">
@@ -4702,10 +4702,10 @@
         <v>344</v>
       </c>
       <c r="E178" t="n">
-        <v>12</v>
+        <v>16.2</v>
       </c>
       <c r="F178" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="179">
@@ -4726,10 +4726,10 @@
         <v>344</v>
       </c>
       <c r="E179" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F179" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="180">
@@ -4750,10 +4750,10 @@
         <v>344</v>
       </c>
       <c r="E180" t="n">
-        <v>12</v>
+        <v>17.2</v>
       </c>
       <c r="F180" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="181">
@@ -4774,10 +4774,10 @@
         <v>344</v>
       </c>
       <c r="E181" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F181" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="182">
@@ -4798,10 +4798,10 @@
         <v>344</v>
       </c>
       <c r="E182" t="n">
-        <v>12</v>
+        <v>14.8</v>
       </c>
       <c r="F182" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="183">
@@ -4822,10 +4822,10 @@
         <v>385</v>
       </c>
       <c r="E183" t="n">
-        <v>18</v>
+        <v>29.7</v>
       </c>
       <c r="F183" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="184">
@@ -4846,10 +4846,10 @@
         <v>384</v>
       </c>
       <c r="E184" t="n">
-        <v>18</v>
+        <v>32.3</v>
       </c>
       <c r="F184" t="n">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="185">
@@ -4870,10 +4870,10 @@
         <v>384</v>
       </c>
       <c r="E185" t="n">
-        <v>18</v>
+        <v>32.4</v>
       </c>
       <c r="F185" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="186">
@@ -4894,10 +4894,10 @@
         <v>386</v>
       </c>
       <c r="E186" t="n">
-        <v>18</v>
+        <v>31.2</v>
       </c>
       <c r="F186" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="187">
@@ -4918,10 +4918,10 @@
         <v>390</v>
       </c>
       <c r="E187" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F187" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="188">
@@ -4942,10 +4942,10 @@
         <v>395</v>
       </c>
       <c r="E188" t="n">
-        <v>18</v>
+        <v>38.7</v>
       </c>
       <c r="F188" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="189">
@@ -4966,10 +4966,10 @@
         <v>400</v>
       </c>
       <c r="E189" t="n">
-        <v>28</v>
+        <v>51.4</v>
       </c>
       <c r="F189" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="190">
@@ -4990,10 +4990,10 @@
         <v>407</v>
       </c>
       <c r="E190" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F190" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="191">
@@ -5014,10 +5014,10 @@
         <v>413</v>
       </c>
       <c r="E191" t="n">
-        <v>28</v>
+        <v>59.7</v>
       </c>
       <c r="F191" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="192">
@@ -5038,10 +5038,10 @@
         <v>420</v>
       </c>
       <c r="E192" t="n">
-        <v>28</v>
+        <v>63.7</v>
       </c>
       <c r="F192" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="193">
@@ -5062,10 +5062,10 @@
         <v>426</v>
       </c>
       <c r="E193" t="n">
-        <v>28</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F193" t="n">
-        <v>1.23</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="194">
@@ -5086,10 +5086,10 @@
         <v>430</v>
       </c>
       <c r="E194" t="n">
-        <v>28</v>
+        <v>74.5</v>
       </c>
       <c r="F194" t="n">
-        <v>1.32</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="195">
@@ -5110,10 +5110,10 @@
         <v>434</v>
       </c>
       <c r="E195" t="n">
-        <v>28</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F195" t="n">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="196">
@@ -5134,10 +5134,10 @@
         <v>436</v>
       </c>
       <c r="E196" t="n">
-        <v>28</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F196" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="197">
@@ -5158,10 +5158,10 @@
         <v>436</v>
       </c>
       <c r="E197" t="n">
-        <v>28</v>
+        <v>76.5</v>
       </c>
       <c r="F197" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="198">
@@ -5182,10 +5182,10 @@
         <v>435</v>
       </c>
       <c r="E198" t="n">
-        <v>28</v>
+        <v>77.2</v>
       </c>
       <c r="F198" t="n">
-        <v>1.24</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="199">
@@ -5206,10 +5206,10 @@
         <v>433</v>
       </c>
       <c r="E199" t="n">
-        <v>28</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F199" t="n">
-        <v>1.36</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="200">
@@ -5230,10 +5230,10 @@
         <v>430</v>
       </c>
       <c r="E200" t="n">
-        <v>28</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F200" t="n">
-        <v>1.3</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="201">
@@ -5254,10 +5254,10 @@
         <v>426</v>
       </c>
       <c r="E201" t="n">
-        <v>28</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F201" t="n">
-        <v>1.14</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -5278,10 +5278,10 @@
         <v>422</v>
       </c>
       <c r="E202" t="n">
-        <v>28</v>
+        <v>67.8</v>
       </c>
       <c r="F202" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="203">
@@ -5302,10 +5302,10 @@
         <v>419</v>
       </c>
       <c r="E203" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="F203" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="204">
@@ -5326,10 +5326,10 @@
         <v>416</v>
       </c>
       <c r="E204" t="n">
-        <v>28</v>
+        <v>61.1</v>
       </c>
       <c r="F204" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="205">
@@ -5350,10 +5350,10 @@
         <v>413</v>
       </c>
       <c r="E205" t="n">
-        <v>28</v>
+        <v>62.3</v>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="206">
@@ -5374,10 +5374,10 @@
         <v>412</v>
       </c>
       <c r="E206" t="n">
-        <v>28</v>
+        <v>59.8</v>
       </c>
       <c r="F206" t="n">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="207">
@@ -5398,10 +5398,10 @@
         <v>411</v>
       </c>
       <c r="E207" t="n">
-        <v>28</v>
+        <v>56.7</v>
       </c>
       <c r="F207" t="n">
-        <v>0.39</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="208">
@@ -5422,10 +5422,10 @@
         <v>410</v>
       </c>
       <c r="E208" t="n">
-        <v>28</v>
+        <v>56.7</v>
       </c>
       <c r="F208" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="209">
@@ -5446,10 +5446,10 @@
         <v>410</v>
       </c>
       <c r="E209" t="n">
-        <v>28</v>
+        <v>58.9</v>
       </c>
       <c r="F209" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="210">
@@ -5470,10 +5470,10 @@
         <v>410</v>
       </c>
       <c r="E210" t="n">
-        <v>28</v>
+        <v>56.3</v>
       </c>
       <c r="F210" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -5494,10 +5494,10 @@
         <v>410</v>
       </c>
       <c r="E211" t="n">
-        <v>28</v>
+        <v>56.7</v>
       </c>
       <c r="F211" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="212">
@@ -5518,7 +5518,7 @@
         <v>409</v>
       </c>
       <c r="E212" t="n">
-        <v>28</v>
+        <v>57.9</v>
       </c>
       <c r="F212" t="n">
         <v>0.71</v>
@@ -5542,10 +5542,10 @@
         <v>408</v>
       </c>
       <c r="E213" t="n">
-        <v>28</v>
+        <v>57.5</v>
       </c>
       <c r="F213" t="n">
-        <v>0.77</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="214">
@@ -5566,10 +5566,10 @@
         <v>406</v>
       </c>
       <c r="E214" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F214" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="215">
@@ -5590,10 +5590,10 @@
         <v>403</v>
       </c>
       <c r="E215" t="n">
-        <v>28</v>
+        <v>52.3</v>
       </c>
       <c r="F215" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="216">
@@ -5614,10 +5614,10 @@
         <v>400</v>
       </c>
       <c r="E216" t="n">
-        <v>28</v>
+        <v>51.9</v>
       </c>
       <c r="F216" t="n">
-        <v>0.66</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="217">
@@ -5638,10 +5638,10 @@
         <v>396</v>
       </c>
       <c r="E217" t="n">
-        <v>18</v>
+        <v>37.6</v>
       </c>
       <c r="F217" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="218">
@@ -5662,10 +5662,10 @@
         <v>393</v>
       </c>
       <c r="E218" t="n">
-        <v>18</v>
+        <v>35.6</v>
       </c>
       <c r="F218" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="219">
@@ -5686,10 +5686,10 @@
         <v>389</v>
       </c>
       <c r="E219" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F219" t="n">
-        <v>0.49</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="220">
@@ -5710,10 +5710,10 @@
         <v>386</v>
       </c>
       <c r="E220" t="n">
-        <v>18</v>
+        <v>32.8</v>
       </c>
       <c r="F220" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="221">
@@ -5734,10 +5734,10 @@
         <v>385</v>
       </c>
       <c r="E221" t="n">
-        <v>18</v>
+        <v>32.4</v>
       </c>
       <c r="F221" t="n">
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="222">
@@ -5758,10 +5758,10 @@
         <v>384</v>
       </c>
       <c r="E222" t="n">
-        <v>18</v>
+        <v>31.2</v>
       </c>
       <c r="F222" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="223">
@@ -5782,10 +5782,10 @@
         <v>385</v>
       </c>
       <c r="E223" t="n">
-        <v>18</v>
+        <v>31.5</v>
       </c>
       <c r="F223" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="224">
@@ -5806,10 +5806,10 @@
         <v>387</v>
       </c>
       <c r="E224" t="n">
-        <v>18</v>
+        <v>31.1</v>
       </c>
       <c r="F224" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="225">
@@ -5830,10 +5830,10 @@
         <v>391</v>
       </c>
       <c r="E225" t="n">
-        <v>18</v>
+        <v>34.7</v>
       </c>
       <c r="F225" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="226">
@@ -5854,10 +5854,10 @@
         <v>396</v>
       </c>
       <c r="E226" t="n">
-        <v>18</v>
+        <v>37.6</v>
       </c>
       <c r="F226" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="227">
@@ -5878,10 +5878,10 @@
         <v>402</v>
       </c>
       <c r="E227" t="n">
-        <v>28</v>
+        <v>51.5</v>
       </c>
       <c r="F227" t="n">
-        <v>0.44</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="228">
@@ -5902,10 +5902,10 @@
         <v>409</v>
       </c>
       <c r="E228" t="n">
-        <v>28</v>
+        <v>59.2</v>
       </c>
       <c r="F228" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="229">
@@ -5926,10 +5926,10 @@
         <v>415</v>
       </c>
       <c r="E229" t="n">
-        <v>28</v>
+        <v>61.7</v>
       </c>
       <c r="F229" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="230">
@@ -5950,10 +5950,10 @@
         <v>422</v>
       </c>
       <c r="E230" t="n">
-        <v>28</v>
+        <v>68.2</v>
       </c>
       <c r="F230" t="n">
-        <v>1.15</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="231">
@@ -5974,10 +5974,10 @@
         <v>427</v>
       </c>
       <c r="E231" t="n">
-        <v>28</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F231" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -5998,10 +5998,10 @@
         <v>431</v>
       </c>
       <c r="E232" t="n">
-        <v>28</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F232" t="n">
-        <v>1.24</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="233">
@@ -6022,10 +6022,10 @@
         <v>434</v>
       </c>
       <c r="E233" t="n">
-        <v>28</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F233" t="n">
-        <v>1.02</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="234">
@@ -6046,10 +6046,10 @@
         <v>436</v>
       </c>
       <c r="E234" t="n">
-        <v>28</v>
+        <v>77.3</v>
       </c>
       <c r="F234" t="n">
-        <v>1.12</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="235">
@@ -6070,10 +6070,10 @@
         <v>436</v>
       </c>
       <c r="E235" t="n">
-        <v>28</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F235" t="n">
-        <v>1.03</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="236">
@@ -6094,10 +6094,10 @@
         <v>434</v>
       </c>
       <c r="E236" t="n">
-        <v>28</v>
+        <v>74.7</v>
       </c>
       <c r="F236" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="237">
@@ -6118,10 +6118,10 @@
         <v>432</v>
       </c>
       <c r="E237" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="F237" t="n">
-        <v>1.19</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="238">
@@ -6142,10 +6142,10 @@
         <v>429</v>
       </c>
       <c r="E238" t="n">
-        <v>28</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F238" t="n">
-        <v>0.76</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="239">
@@ -6166,10 +6166,10 @@
         <v>425</v>
       </c>
       <c r="E239" t="n">
-        <v>28</v>
+        <v>67.3</v>
       </c>
       <c r="F239" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="240">
@@ -6190,10 +6190,10 @@
         <v>421</v>
       </c>
       <c r="E240" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="F240" t="n">
-        <v>0.95</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="241">
@@ -6214,10 +6214,10 @@
         <v>418</v>
       </c>
       <c r="E241" t="n">
-        <v>28</v>
+        <v>62.7</v>
       </c>
       <c r="F241" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="242">
@@ -6238,10 +6238,10 @@
         <v>415</v>
       </c>
       <c r="E242" t="n">
-        <v>28</v>
+        <v>63.6</v>
       </c>
       <c r="F242" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="243">
@@ -6262,10 +6262,10 @@
         <v>413</v>
       </c>
       <c r="E243" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F243" t="n">
-        <v>1.02</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="244">
@@ -6286,10 +6286,10 @@
         <v>411</v>
       </c>
       <c r="E244" t="n">
-        <v>28</v>
+        <v>60.8</v>
       </c>
       <c r="F244" t="n">
-        <v>0.97</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="245">
@@ -6310,10 +6310,10 @@
         <v>410</v>
       </c>
       <c r="E245" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="F245" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="246">
@@ -6334,10 +6334,10 @@
         <v>410</v>
       </c>
       <c r="E246" t="n">
-        <v>28</v>
+        <v>56.4</v>
       </c>
       <c r="F246" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="247">
@@ -6358,10 +6358,10 @@
         <v>410</v>
       </c>
       <c r="E247" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F247" t="n">
-        <v>0.96</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="248">
@@ -6382,10 +6382,10 @@
         <v>410</v>
       </c>
       <c r="E248" t="n">
-        <v>28</v>
+        <v>57.9</v>
       </c>
       <c r="F248" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="249">
@@ -6406,10 +6406,10 @@
         <v>410</v>
       </c>
       <c r="E249" t="n">
-        <v>28</v>
+        <v>59.9</v>
       </c>
       <c r="F249" t="n">
-        <v>0.97</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="250">
@@ -6430,10 +6430,10 @@
         <v>409</v>
       </c>
       <c r="E250" t="n">
-        <v>28</v>
+        <v>59.3</v>
       </c>
       <c r="F250" t="n">
-        <v>0.96</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="251">
@@ -6454,10 +6454,10 @@
         <v>407</v>
       </c>
       <c r="E251" t="n">
-        <v>28</v>
+        <v>57.8</v>
       </c>
       <c r="F251" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="252">
@@ -6478,10 +6478,10 @@
         <v>405</v>
       </c>
       <c r="E252" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F252" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="253">
@@ -6502,10 +6502,10 @@
         <v>402</v>
       </c>
       <c r="E253" t="n">
-        <v>28</v>
+        <v>52.3</v>
       </c>
       <c r="F253" t="n">
-        <v>0.52</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="254">
@@ -6526,10 +6526,10 @@
         <v>399</v>
       </c>
       <c r="E254" t="n">
-        <v>18</v>
+        <v>41.8</v>
       </c>
       <c r="F254" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="255">
@@ -6550,10 +6550,10 @@
         <v>395</v>
       </c>
       <c r="E255" t="n">
-        <v>18</v>
+        <v>37.2</v>
       </c>
       <c r="F255" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="256">
@@ -6574,10 +6574,10 @@
         <v>392</v>
       </c>
       <c r="E256" t="n">
-        <v>18</v>
+        <v>34.2</v>
       </c>
       <c r="F256" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="257">
@@ -6598,10 +6598,10 @@
         <v>388</v>
       </c>
       <c r="E257" t="n">
-        <v>18</v>
+        <v>33.6</v>
       </c>
       <c r="F257" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="258">
@@ -6622,10 +6622,10 @@
         <v>386</v>
       </c>
       <c r="E258" t="n">
-        <v>18</v>
+        <v>33.5</v>
       </c>
       <c r="F258" t="n">
-        <v>0.49</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="259">
@@ -6646,10 +6646,10 @@
         <v>384</v>
       </c>
       <c r="E259" t="n">
-        <v>18</v>
+        <v>31.6</v>
       </c>
       <c r="F259" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="260">
@@ -6670,10 +6670,10 @@
         <v>384</v>
       </c>
       <c r="E260" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F260" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="261">
@@ -6694,10 +6694,10 @@
         <v>385</v>
       </c>
       <c r="E261" t="n">
-        <v>18</v>
+        <v>29.9</v>
       </c>
       <c r="F261" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="262">
@@ -6718,10 +6718,10 @@
         <v>388</v>
       </c>
       <c r="E262" t="n">
-        <v>18</v>
+        <v>33.8</v>
       </c>
       <c r="F262" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="263">
@@ -6742,10 +6742,10 @@
         <v>393</v>
       </c>
       <c r="E263" t="n">
-        <v>18</v>
+        <v>38.1</v>
       </c>
       <c r="F263" t="n">
-        <v>0.65</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="264">
@@ -6766,10 +6766,10 @@
         <v>398</v>
       </c>
       <c r="E264" t="n">
-        <v>18</v>
+        <v>38.2</v>
       </c>
       <c r="F264" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="265">
@@ -6790,10 +6790,10 @@
         <v>404</v>
       </c>
       <c r="E265" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F265" t="n">
-        <v>0.62</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="266">
@@ -6814,10 +6814,10 @@
         <v>411</v>
       </c>
       <c r="E266" t="n">
-        <v>28</v>
+        <v>60.3</v>
       </c>
       <c r="F266" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="267">
@@ -6838,10 +6838,10 @@
         <v>417</v>
       </c>
       <c r="E267" t="n">
-        <v>28</v>
+        <v>64.5</v>
       </c>
       <c r="F267" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="268">
@@ -6862,10 +6862,10 @@
         <v>423</v>
       </c>
       <c r="E268" t="n">
-        <v>28</v>
+        <v>68.7</v>
       </c>
       <c r="F268" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="269">
@@ -6886,10 +6886,10 @@
         <v>428</v>
       </c>
       <c r="E269" t="n">
-        <v>28</v>
+        <v>72.5</v>
       </c>
       <c r="F269" t="n">
-        <v>1.12</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -6910,10 +6910,10 @@
         <v>432</v>
       </c>
       <c r="E270" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F270" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="271">
@@ -6934,10 +6934,10 @@
         <v>435</v>
       </c>
       <c r="E271" t="n">
-        <v>28</v>
+        <v>75.5</v>
       </c>
       <c r="F271" t="n">
-        <v>0.84</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="272">
@@ -6958,10 +6958,10 @@
         <v>436</v>
       </c>
       <c r="E272" t="n">
-        <v>28</v>
+        <v>78.3</v>
       </c>
       <c r="F272" t="n">
-        <v>1.34</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="273">
@@ -6982,10 +6982,10 @@
         <v>436</v>
       </c>
       <c r="E273" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="F273" t="n">
-        <v>1.33</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="274">
@@ -7006,10 +7006,10 @@
         <v>434</v>
       </c>
       <c r="E274" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="F274" t="n">
-        <v>1.35</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="275">
@@ -7030,10 +7030,10 @@
         <v>319</v>
       </c>
       <c r="E275" t="n">
-        <v>8</v>
+        <v>10.8</v>
       </c>
       <c r="F275" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="276">
@@ -7054,10 +7054,10 @@
         <v>319</v>
       </c>
       <c r="E276" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="F276" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="277">
@@ -7078,10 +7078,10 @@
         <v>319</v>
       </c>
       <c r="E277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F277" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="278">
@@ -7102,10 +7102,10 @@
         <v>319</v>
       </c>
       <c r="E278" t="n">
-        <v>8</v>
+        <v>10.1</v>
       </c>
       <c r="F278" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="279">
@@ -7126,10 +7126,10 @@
         <v>318</v>
       </c>
       <c r="E279" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="F279" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="280">
@@ -7150,10 +7150,10 @@
         <v>318</v>
       </c>
       <c r="E280" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="F280" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="281">
@@ -7174,10 +7174,10 @@
         <v>318</v>
       </c>
       <c r="E281" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="F281" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="282">
@@ -7198,10 +7198,10 @@
         <v>318</v>
       </c>
       <c r="E282" t="n">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="F282" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="283">
@@ -7225,7 +7225,7 @@
         <v>8</v>
       </c>
       <c r="F283" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="284">
@@ -7246,10 +7246,10 @@
         <v>318</v>
       </c>
       <c r="E284" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F284" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="285">
@@ -7270,10 +7270,10 @@
         <v>318</v>
       </c>
       <c r="E285" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F285" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="286">
@@ -7294,10 +7294,10 @@
         <v>318</v>
       </c>
       <c r="E286" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="F286" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="287">
@@ -7318,10 +7318,10 @@
         <v>318</v>
       </c>
       <c r="E287" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="F287" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="288">
@@ -7342,10 +7342,10 @@
         <v>318</v>
       </c>
       <c r="E288" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="F288" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="289">
@@ -7366,10 +7366,10 @@
         <v>318</v>
       </c>
       <c r="E289" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="F289" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="290">
@@ -7390,10 +7390,10 @@
         <v>318</v>
       </c>
       <c r="E290" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F290" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="291">
@@ -7414,10 +7414,10 @@
         <v>319</v>
       </c>
       <c r="E291" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F291" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="292">
@@ -7438,10 +7438,10 @@
         <v>319</v>
       </c>
       <c r="E292" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F292" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="293">
@@ -7462,10 +7462,10 @@
         <v>319</v>
       </c>
       <c r="E293" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="F293" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="294">
@@ -7486,10 +7486,10 @@
         <v>319</v>
       </c>
       <c r="E294" t="n">
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="F294" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="295">
@@ -7510,10 +7510,10 @@
         <v>319</v>
       </c>
       <c r="E295" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F295" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="296">
@@ -7534,10 +7534,10 @@
         <v>320</v>
       </c>
       <c r="E296" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="F296" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="297">
@@ -7558,10 +7558,10 @@
         <v>320</v>
       </c>
       <c r="E297" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="F297" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="298">
@@ -7582,10 +7582,10 @@
         <v>320</v>
       </c>
       <c r="E298" t="n">
-        <v>12</v>
+        <v>15.9</v>
       </c>
       <c r="F298" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="299">
@@ -7606,10 +7606,10 @@
         <v>321</v>
       </c>
       <c r="E299" t="n">
-        <v>12</v>
+        <v>13.9</v>
       </c>
       <c r="F299" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="300">
@@ -7630,10 +7630,10 @@
         <v>321</v>
       </c>
       <c r="E300" t="n">
-        <v>12</v>
+        <v>15.7</v>
       </c>
       <c r="F300" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="301">
@@ -7654,10 +7654,10 @@
         <v>321</v>
       </c>
       <c r="E301" t="n">
-        <v>12</v>
+        <v>13.7</v>
       </c>
       <c r="F301" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="302">
@@ -7678,10 +7678,10 @@
         <v>321</v>
       </c>
       <c r="E302" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="F302" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="303">
@@ -7702,10 +7702,10 @@
         <v>322</v>
       </c>
       <c r="E303" t="n">
-        <v>12</v>
+        <v>15.9</v>
       </c>
       <c r="F303" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="304">
@@ -7726,10 +7726,10 @@
         <v>322</v>
       </c>
       <c r="E304" t="n">
-        <v>12</v>
+        <v>16.1</v>
       </c>
       <c r="F304" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="305">
@@ -7750,10 +7750,10 @@
         <v>322</v>
       </c>
       <c r="E305" t="n">
-        <v>12</v>
+        <v>16.7</v>
       </c>
       <c r="F305" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="306">
@@ -7774,10 +7774,10 @@
         <v>323</v>
       </c>
       <c r="E306" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="F306" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="307">
@@ -7798,10 +7798,10 @@
         <v>323</v>
       </c>
       <c r="E307" t="n">
-        <v>12</v>
+        <v>18.4</v>
       </c>
       <c r="F307" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="308">
@@ -7822,7 +7822,7 @@
         <v>323</v>
       </c>
       <c r="E308" t="n">
-        <v>12</v>
+        <v>16.8</v>
       </c>
       <c r="F308" t="n">
         <v>0.19</v>
@@ -7846,10 +7846,10 @@
         <v>324</v>
       </c>
       <c r="E309" t="n">
-        <v>12</v>
+        <v>16.2</v>
       </c>
       <c r="F309" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="310">
@@ -7870,10 +7870,10 @@
         <v>324</v>
       </c>
       <c r="E310" t="n">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="F310" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="311">
@@ -7894,10 +7894,10 @@
         <v>324</v>
       </c>
       <c r="E311" t="n">
-        <v>12</v>
+        <v>16.3</v>
       </c>
       <c r="F311" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="312">
@@ -7918,10 +7918,10 @@
         <v>325</v>
       </c>
       <c r="E312" t="n">
-        <v>12</v>
+        <v>17.1</v>
       </c>
       <c r="F312" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="313">
@@ -7942,10 +7942,10 @@
         <v>325</v>
       </c>
       <c r="E313" t="n">
-        <v>12</v>
+        <v>15.8</v>
       </c>
       <c r="F313" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="314">
@@ -7966,10 +7966,10 @@
         <v>325</v>
       </c>
       <c r="E314" t="n">
-        <v>12</v>
+        <v>15.8</v>
       </c>
       <c r="F314" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="315">
@@ -7990,10 +7990,10 @@
         <v>325</v>
       </c>
       <c r="E315" t="n">
-        <v>12</v>
+        <v>19.6</v>
       </c>
       <c r="F315" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="316">
@@ -8014,10 +8014,10 @@
         <v>325</v>
       </c>
       <c r="E316" t="n">
-        <v>12</v>
+        <v>19.2</v>
       </c>
       <c r="F316" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="317">
@@ -8038,10 +8038,10 @@
         <v>326</v>
       </c>
       <c r="E317" t="n">
-        <v>12</v>
+        <v>18.8</v>
       </c>
       <c r="F317" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="318">
@@ -8062,10 +8062,10 @@
         <v>326</v>
       </c>
       <c r="E318" t="n">
-        <v>12</v>
+        <v>17.7</v>
       </c>
       <c r="F318" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="319">
@@ -8086,10 +8086,10 @@
         <v>326</v>
       </c>
       <c r="E319" t="n">
-        <v>12</v>
+        <v>16.8</v>
       </c>
       <c r="F319" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="320">
@@ -8110,10 +8110,10 @@
         <v>326</v>
       </c>
       <c r="E320" t="n">
-        <v>12</v>
+        <v>16.8</v>
       </c>
       <c r="F320" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="321">
@@ -8134,10 +8134,10 @@
         <v>326</v>
       </c>
       <c r="E321" t="n">
-        <v>12</v>
+        <v>17.2</v>
       </c>
       <c r="F321" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="322">
@@ -8158,10 +8158,10 @@
         <v>326</v>
       </c>
       <c r="E322" t="n">
-        <v>12</v>
+        <v>18.4</v>
       </c>
       <c r="F322" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="323">
@@ -8182,10 +8182,10 @@
         <v>326</v>
       </c>
       <c r="E323" t="n">
-        <v>12</v>
+        <v>19.1</v>
       </c>
       <c r="F323" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="324">
@@ -8206,10 +8206,10 @@
         <v>326</v>
       </c>
       <c r="E324" t="n">
-        <v>12</v>
+        <v>18.8</v>
       </c>
       <c r="F324" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="325">
@@ -8230,10 +8230,10 @@
         <v>326</v>
       </c>
       <c r="E325" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="F325" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="326">
@@ -8254,10 +8254,10 @@
         <v>326</v>
       </c>
       <c r="E326" t="n">
-        <v>12</v>
+        <v>19.9</v>
       </c>
       <c r="F326" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="327">
@@ -8278,10 +8278,10 @@
         <v>326</v>
       </c>
       <c r="E327" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F327" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="328">
@@ -8302,10 +8302,10 @@
         <v>326</v>
       </c>
       <c r="E328" t="n">
-        <v>12</v>
+        <v>18.2</v>
       </c>
       <c r="F328" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="329">
@@ -8326,10 +8326,10 @@
         <v>325</v>
       </c>
       <c r="E329" t="n">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="F329" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="330">
@@ -8350,10 +8350,10 @@
         <v>325</v>
       </c>
       <c r="E330" t="n">
-        <v>12</v>
+        <v>17.4</v>
       </c>
       <c r="F330" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="331">
@@ -8374,10 +8374,10 @@
         <v>325</v>
       </c>
       <c r="E331" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="F331" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="332">
@@ -8398,10 +8398,10 @@
         <v>325</v>
       </c>
       <c r="E332" t="n">
-        <v>12</v>
+        <v>16.9</v>
       </c>
       <c r="F332" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="333">
@@ -8422,10 +8422,10 @@
         <v>325</v>
       </c>
       <c r="E333" t="n">
-        <v>12</v>
+        <v>18.4</v>
       </c>
       <c r="F333" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="334">
@@ -8446,7 +8446,7 @@
         <v>324</v>
       </c>
       <c r="E334" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="F334" t="n">
         <v>0.15</v>
@@ -8470,10 +8470,10 @@
         <v>324</v>
       </c>
       <c r="E335" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="F335" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="336">
@@ -8494,10 +8494,10 @@
         <v>324</v>
       </c>
       <c r="E336" t="n">
-        <v>12</v>
+        <v>15.1</v>
       </c>
       <c r="F336" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="337">
@@ -8518,10 +8518,10 @@
         <v>323</v>
       </c>
       <c r="E337" t="n">
-        <v>12</v>
+        <v>14.9</v>
       </c>
       <c r="F337" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="338">
@@ -8542,10 +8542,10 @@
         <v>323</v>
       </c>
       <c r="E338" t="n">
-        <v>12</v>
+        <v>17.9</v>
       </c>
       <c r="F338" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="339">
@@ -8566,10 +8566,10 @@
         <v>323</v>
       </c>
       <c r="E339" t="n">
-        <v>12</v>
+        <v>17.2</v>
       </c>
       <c r="F339" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="340">
@@ -8590,10 +8590,10 @@
         <v>322</v>
       </c>
       <c r="E340" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F340" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="341">
@@ -8614,10 +8614,10 @@
         <v>322</v>
       </c>
       <c r="E341" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
       <c r="F341" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="342">
@@ -8638,10 +8638,10 @@
         <v>322</v>
       </c>
       <c r="E342" t="n">
-        <v>12</v>
+        <v>15.7</v>
       </c>
       <c r="F342" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="343">
@@ -8662,10 +8662,10 @@
         <v>321</v>
       </c>
       <c r="E343" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="F343" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="344">
@@ -8686,7 +8686,7 @@
         <v>321</v>
       </c>
       <c r="E344" t="n">
-        <v>12</v>
+        <v>14.1</v>
       </c>
       <c r="F344" t="n">
         <v>0.15</v>
@@ -8710,10 +8710,10 @@
         <v>321</v>
       </c>
       <c r="E345" t="n">
-        <v>12</v>
+        <v>14.9</v>
       </c>
       <c r="F345" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="346">
@@ -8734,10 +8734,10 @@
         <v>320</v>
       </c>
       <c r="E346" t="n">
-        <v>12</v>
+        <v>14.6</v>
       </c>
       <c r="F346" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="347">
@@ -8758,10 +8758,10 @@
         <v>320</v>
       </c>
       <c r="E347" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="F347" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="348">
@@ -8782,10 +8782,10 @@
         <v>320</v>
       </c>
       <c r="E348" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F348" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="349">
@@ -8806,10 +8806,10 @@
         <v>320</v>
       </c>
       <c r="E349" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F349" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="350">
@@ -8830,10 +8830,10 @@
         <v>319</v>
       </c>
       <c r="E350" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F350" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="351">
@@ -8854,10 +8854,10 @@
         <v>319</v>
       </c>
       <c r="E351" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="F351" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="352">
@@ -8878,10 +8878,10 @@
         <v>319</v>
       </c>
       <c r="E352" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F352" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="353">
@@ -8902,10 +8902,10 @@
         <v>319</v>
       </c>
       <c r="E353" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="F353" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="354">
@@ -8926,10 +8926,10 @@
         <v>319</v>
       </c>
       <c r="E354" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="F354" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="355">
@@ -8950,10 +8950,10 @@
         <v>318</v>
       </c>
       <c r="E355" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="F355" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="356">
@@ -8974,10 +8974,10 @@
         <v>318</v>
       </c>
       <c r="E356" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F356" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="357">
@@ -8998,10 +8998,10 @@
         <v>318</v>
       </c>
       <c r="E357" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F357" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="358">
@@ -9022,10 +9022,10 @@
         <v>318</v>
       </c>
       <c r="E358" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="F358" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="359">
@@ -9046,10 +9046,10 @@
         <v>318</v>
       </c>
       <c r="E359" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F359" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="360">
@@ -9070,10 +9070,10 @@
         <v>318</v>
       </c>
       <c r="E360" t="n">
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="F360" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="361">
@@ -9094,10 +9094,10 @@
         <v>318</v>
       </c>
       <c r="E361" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="F361" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="362">
@@ -9118,10 +9118,10 @@
         <v>318</v>
       </c>
       <c r="E362" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F362" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="363">
@@ -9142,10 +9142,10 @@
         <v>318</v>
       </c>
       <c r="E363" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F363" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="364">
@@ -9166,10 +9166,10 @@
         <v>318</v>
       </c>
       <c r="E364" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="F364" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="365">
@@ -9190,10 +9190,10 @@
         <v>318</v>
       </c>
       <c r="E365" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="F365" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="366">
@@ -9214,10 +9214,10 @@
         <v>318</v>
       </c>
       <c r="E366" t="n">
-        <v>8</v>
+        <v>10.6</v>
       </c>
       <c r="F366" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
